--- a/ISF 10+2 Filing Form.xlsx
+++ b/ISF 10+2 Filing Form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aafc9cdea5a265a1/Desktop/Daily Ops Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{9059B557-F272-4946-B306-36D0BC3810F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F9A919-22E7-4D39-B0D4-D0872CA13703}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{9059B557-F272-4946-B306-36D0BC3810F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5548A0B-2578-4BBD-A819-2F2667202FF4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C419247C-0A35-428D-B2B5-560F94F7A46B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C419247C-0A35-428D-B2B5-560F94F7A46B}"/>
   </bookViews>
   <sheets>
     <sheet name="ISF 10+2 Filing" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>ISF 10+2 Filing Form</t>
   </si>
@@ -241,114 +241,12 @@
       <t xml:space="preserve"> before loading. Failure to comply with this requirement may result in penalties being assessed by US Customs against the Importer of Record. </t>
     </r>
   </si>
-  <si>
-    <t>OCBS S01255814</t>
-  </si>
-  <si>
-    <t>HLCUAKL260100659</t>
-  </si>
-  <si>
-    <t>LCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANL WARRNAMBOOL </t>
-  </si>
-  <si>
-    <t>604N</t>
-  </si>
-  <si>
-    <t>UACU5725466</t>
-  </si>
-  <si>
-    <t>TAURANGA</t>
-  </si>
-  <si>
-    <t>LONG BEACH</t>
-  </si>
-  <si>
-    <t>KAYSHAN INTERNATIONAL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 390 HILLSBOROUGH ROAD MOUNT ROSKILL</t>
-  </si>
-  <si>
-    <t>AUCKLAND NZ</t>
-  </si>
-  <si>
-    <t>IUSR – AWD 3PL (Cowpens, SC, US)</t>
-  </si>
-  <si>
-    <t>1120 Mt Olive Rd</t>
-  </si>
-  <si>
-    <t>COWPENS,</t>
-  </si>
-  <si>
-    <t>SC 29330</t>
-  </si>
-  <si>
-    <t>AMAZON INC</t>
-  </si>
-  <si>
-    <t>3105.90.0050</t>
-  </si>
-  <si>
-    <t>ROOTBLAST</t>
-  </si>
-  <si>
-    <t>242704-58232</t>
-  </si>
-  <si>
-    <t>NZ</t>
-  </si>
-  <si>
-    <r>
-      <t>ACFS PORT LOGISTICS NZ LTD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">373a Neilson Street, </t>
-  </si>
-  <si>
-    <t>Penrose , Auckland 1061</t>
-  </si>
-  <si>
-    <t>25 Anzac Street</t>
-  </si>
-  <si>
-    <r>
-      <t>Oceanbridge Shipping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, , </t>
-    </r>
-  </si>
-  <si>
-    <t>Takapuna AKL 0622 NZ</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,13 +332,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
@@ -937,6 +828,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -974,10 +869,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1294,393 +1185,380 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DA4C6C0-F524-479E-87D4-4363DC222A36}">
   <dimension ref="A1:WVL44"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-    <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
-    <col min="5" max="256" width="8.81640625" hidden="1"/>
+    <col min="5" max="256" width="8.85546875" hidden="1"/>
     <col min="257" max="257" width="27" hidden="1"/>
-    <col min="258" max="258" width="35.1796875" hidden="1"/>
-    <col min="259" max="259" width="23.7265625" hidden="1"/>
+    <col min="258" max="258" width="35.140625" hidden="1"/>
+    <col min="259" max="259" width="23.7109375" hidden="1"/>
     <col min="260" max="260" width="43" hidden="1"/>
-    <col min="261" max="512" width="8.81640625" hidden="1"/>
+    <col min="261" max="512" width="8.85546875" hidden="1"/>
     <col min="513" max="513" width="27" hidden="1"/>
-    <col min="514" max="514" width="35.1796875" hidden="1"/>
-    <col min="515" max="515" width="23.7265625" hidden="1"/>
+    <col min="514" max="514" width="35.140625" hidden="1"/>
+    <col min="515" max="515" width="23.7109375" hidden="1"/>
     <col min="516" max="516" width="43" hidden="1"/>
-    <col min="517" max="768" width="8.81640625" hidden="1"/>
+    <col min="517" max="768" width="8.85546875" hidden="1"/>
     <col min="769" max="769" width="27" hidden="1"/>
-    <col min="770" max="770" width="35.1796875" hidden="1"/>
-    <col min="771" max="771" width="23.7265625" hidden="1"/>
+    <col min="770" max="770" width="35.140625" hidden="1"/>
+    <col min="771" max="771" width="23.7109375" hidden="1"/>
     <col min="772" max="772" width="43" hidden="1"/>
-    <col min="773" max="1024" width="8.81640625" hidden="1"/>
+    <col min="773" max="1024" width="8.85546875" hidden="1"/>
     <col min="1025" max="1025" width="27" hidden="1"/>
-    <col min="1026" max="1026" width="35.1796875" hidden="1"/>
-    <col min="1027" max="1027" width="23.7265625" hidden="1"/>
+    <col min="1026" max="1026" width="35.140625" hidden="1"/>
+    <col min="1027" max="1027" width="23.7109375" hidden="1"/>
     <col min="1028" max="1028" width="43" hidden="1"/>
-    <col min="1029" max="1280" width="8.81640625" hidden="1"/>
+    <col min="1029" max="1280" width="8.85546875" hidden="1"/>
     <col min="1281" max="1281" width="27" hidden="1"/>
-    <col min="1282" max="1282" width="35.1796875" hidden="1"/>
-    <col min="1283" max="1283" width="23.7265625" hidden="1"/>
+    <col min="1282" max="1282" width="35.140625" hidden="1"/>
+    <col min="1283" max="1283" width="23.7109375" hidden="1"/>
     <col min="1284" max="1284" width="43" hidden="1"/>
-    <col min="1285" max="1536" width="8.81640625" hidden="1"/>
+    <col min="1285" max="1536" width="8.85546875" hidden="1"/>
     <col min="1537" max="1537" width="27" hidden="1"/>
-    <col min="1538" max="1538" width="35.1796875" hidden="1"/>
-    <col min="1539" max="1539" width="23.7265625" hidden="1"/>
+    <col min="1538" max="1538" width="35.140625" hidden="1"/>
+    <col min="1539" max="1539" width="23.7109375" hidden="1"/>
     <col min="1540" max="1540" width="43" hidden="1"/>
-    <col min="1541" max="1792" width="8.81640625" hidden="1"/>
+    <col min="1541" max="1792" width="8.85546875" hidden="1"/>
     <col min="1793" max="1793" width="27" hidden="1"/>
-    <col min="1794" max="1794" width="35.1796875" hidden="1"/>
-    <col min="1795" max="1795" width="23.7265625" hidden="1"/>
+    <col min="1794" max="1794" width="35.140625" hidden="1"/>
+    <col min="1795" max="1795" width="23.7109375" hidden="1"/>
     <col min="1796" max="1796" width="43" hidden="1"/>
-    <col min="1797" max="2048" width="8.81640625" hidden="1"/>
+    <col min="1797" max="2048" width="8.85546875" hidden="1"/>
     <col min="2049" max="2049" width="27" hidden="1"/>
-    <col min="2050" max="2050" width="35.1796875" hidden="1"/>
-    <col min="2051" max="2051" width="23.7265625" hidden="1"/>
+    <col min="2050" max="2050" width="35.140625" hidden="1"/>
+    <col min="2051" max="2051" width="23.7109375" hidden="1"/>
     <col min="2052" max="2052" width="43" hidden="1"/>
-    <col min="2053" max="2304" width="8.81640625" hidden="1"/>
+    <col min="2053" max="2304" width="8.85546875" hidden="1"/>
     <col min="2305" max="2305" width="27" hidden="1"/>
-    <col min="2306" max="2306" width="35.1796875" hidden="1"/>
-    <col min="2307" max="2307" width="23.7265625" hidden="1"/>
+    <col min="2306" max="2306" width="35.140625" hidden="1"/>
+    <col min="2307" max="2307" width="23.7109375" hidden="1"/>
     <col min="2308" max="2308" width="43" hidden="1"/>
-    <col min="2309" max="2560" width="8.81640625" hidden="1"/>
+    <col min="2309" max="2560" width="8.85546875" hidden="1"/>
     <col min="2561" max="2561" width="27" hidden="1"/>
-    <col min="2562" max="2562" width="35.1796875" hidden="1"/>
-    <col min="2563" max="2563" width="23.7265625" hidden="1"/>
+    <col min="2562" max="2562" width="35.140625" hidden="1"/>
+    <col min="2563" max="2563" width="23.7109375" hidden="1"/>
     <col min="2564" max="2564" width="43" hidden="1"/>
-    <col min="2565" max="2816" width="8.81640625" hidden="1"/>
+    <col min="2565" max="2816" width="8.85546875" hidden="1"/>
     <col min="2817" max="2817" width="27" hidden="1"/>
-    <col min="2818" max="2818" width="35.1796875" hidden="1"/>
-    <col min="2819" max="2819" width="23.7265625" hidden="1"/>
+    <col min="2818" max="2818" width="35.140625" hidden="1"/>
+    <col min="2819" max="2819" width="23.7109375" hidden="1"/>
     <col min="2820" max="2820" width="43" hidden="1"/>
-    <col min="2821" max="3072" width="8.81640625" hidden="1"/>
+    <col min="2821" max="3072" width="8.85546875" hidden="1"/>
     <col min="3073" max="3073" width="27" hidden="1"/>
-    <col min="3074" max="3074" width="35.1796875" hidden="1"/>
-    <col min="3075" max="3075" width="23.7265625" hidden="1"/>
+    <col min="3074" max="3074" width="35.140625" hidden="1"/>
+    <col min="3075" max="3075" width="23.7109375" hidden="1"/>
     <col min="3076" max="3076" width="43" hidden="1"/>
-    <col min="3077" max="3328" width="8.81640625" hidden="1"/>
+    <col min="3077" max="3328" width="8.85546875" hidden="1"/>
     <col min="3329" max="3329" width="27" hidden="1"/>
-    <col min="3330" max="3330" width="35.1796875" hidden="1"/>
-    <col min="3331" max="3331" width="23.7265625" hidden="1"/>
+    <col min="3330" max="3330" width="35.140625" hidden="1"/>
+    <col min="3331" max="3331" width="23.7109375" hidden="1"/>
     <col min="3332" max="3332" width="43" hidden="1"/>
-    <col min="3333" max="3584" width="8.81640625" hidden="1"/>
+    <col min="3333" max="3584" width="8.85546875" hidden="1"/>
     <col min="3585" max="3585" width="27" hidden="1"/>
-    <col min="3586" max="3586" width="35.1796875" hidden="1"/>
-    <col min="3587" max="3587" width="23.7265625" hidden="1"/>
+    <col min="3586" max="3586" width="35.140625" hidden="1"/>
+    <col min="3587" max="3587" width="23.7109375" hidden="1"/>
     <col min="3588" max="3588" width="43" hidden="1"/>
-    <col min="3589" max="3840" width="8.81640625" hidden="1"/>
+    <col min="3589" max="3840" width="8.85546875" hidden="1"/>
     <col min="3841" max="3841" width="27" hidden="1"/>
-    <col min="3842" max="3842" width="35.1796875" hidden="1"/>
-    <col min="3843" max="3843" width="23.7265625" hidden="1"/>
+    <col min="3842" max="3842" width="35.140625" hidden="1"/>
+    <col min="3843" max="3843" width="23.7109375" hidden="1"/>
     <col min="3844" max="3844" width="43" hidden="1"/>
-    <col min="3845" max="4096" width="8.81640625" hidden="1"/>
+    <col min="3845" max="4096" width="8.85546875" hidden="1"/>
     <col min="4097" max="4097" width="27" hidden="1"/>
-    <col min="4098" max="4098" width="35.1796875" hidden="1"/>
-    <col min="4099" max="4099" width="23.7265625" hidden="1"/>
+    <col min="4098" max="4098" width="35.140625" hidden="1"/>
+    <col min="4099" max="4099" width="23.7109375" hidden="1"/>
     <col min="4100" max="4100" width="43" hidden="1"/>
-    <col min="4101" max="4352" width="8.81640625" hidden="1"/>
+    <col min="4101" max="4352" width="8.85546875" hidden="1"/>
     <col min="4353" max="4353" width="27" hidden="1"/>
-    <col min="4354" max="4354" width="35.1796875" hidden="1"/>
-    <col min="4355" max="4355" width="23.7265625" hidden="1"/>
+    <col min="4354" max="4354" width="35.140625" hidden="1"/>
+    <col min="4355" max="4355" width="23.7109375" hidden="1"/>
     <col min="4356" max="4356" width="43" hidden="1"/>
-    <col min="4357" max="4608" width="8.81640625" hidden="1"/>
+    <col min="4357" max="4608" width="8.85546875" hidden="1"/>
     <col min="4609" max="4609" width="27" hidden="1"/>
-    <col min="4610" max="4610" width="35.1796875" hidden="1"/>
-    <col min="4611" max="4611" width="23.7265625" hidden="1"/>
+    <col min="4610" max="4610" width="35.140625" hidden="1"/>
+    <col min="4611" max="4611" width="23.7109375" hidden="1"/>
     <col min="4612" max="4612" width="43" hidden="1"/>
-    <col min="4613" max="4864" width="8.81640625" hidden="1"/>
+    <col min="4613" max="4864" width="8.85546875" hidden="1"/>
     <col min="4865" max="4865" width="27" hidden="1"/>
-    <col min="4866" max="4866" width="35.1796875" hidden="1"/>
-    <col min="4867" max="4867" width="23.7265625" hidden="1"/>
+    <col min="4866" max="4866" width="35.140625" hidden="1"/>
+    <col min="4867" max="4867" width="23.7109375" hidden="1"/>
     <col min="4868" max="4868" width="43" hidden="1"/>
-    <col min="4869" max="5120" width="8.81640625" hidden="1"/>
+    <col min="4869" max="5120" width="8.85546875" hidden="1"/>
     <col min="5121" max="5121" width="27" hidden="1"/>
-    <col min="5122" max="5122" width="35.1796875" hidden="1"/>
-    <col min="5123" max="5123" width="23.7265625" hidden="1"/>
+    <col min="5122" max="5122" width="35.140625" hidden="1"/>
+    <col min="5123" max="5123" width="23.7109375" hidden="1"/>
     <col min="5124" max="5124" width="43" hidden="1"/>
-    <col min="5125" max="5376" width="8.81640625" hidden="1"/>
+    <col min="5125" max="5376" width="8.85546875" hidden="1"/>
     <col min="5377" max="5377" width="27" hidden="1"/>
-    <col min="5378" max="5378" width="35.1796875" hidden="1"/>
-    <col min="5379" max="5379" width="23.7265625" hidden="1"/>
+    <col min="5378" max="5378" width="35.140625" hidden="1"/>
+    <col min="5379" max="5379" width="23.7109375" hidden="1"/>
     <col min="5380" max="5380" width="43" hidden="1"/>
-    <col min="5381" max="5632" width="8.81640625" hidden="1"/>
+    <col min="5381" max="5632" width="8.85546875" hidden="1"/>
     <col min="5633" max="5633" width="27" hidden="1"/>
-    <col min="5634" max="5634" width="35.1796875" hidden="1"/>
-    <col min="5635" max="5635" width="23.7265625" hidden="1"/>
+    <col min="5634" max="5634" width="35.140625" hidden="1"/>
+    <col min="5635" max="5635" width="23.7109375" hidden="1"/>
     <col min="5636" max="5636" width="43" hidden="1"/>
-    <col min="5637" max="5888" width="8.81640625" hidden="1"/>
+    <col min="5637" max="5888" width="8.85546875" hidden="1"/>
     <col min="5889" max="5889" width="27" hidden="1"/>
-    <col min="5890" max="5890" width="35.1796875" hidden="1"/>
-    <col min="5891" max="5891" width="23.7265625" hidden="1"/>
+    <col min="5890" max="5890" width="35.140625" hidden="1"/>
+    <col min="5891" max="5891" width="23.7109375" hidden="1"/>
     <col min="5892" max="5892" width="43" hidden="1"/>
-    <col min="5893" max="6144" width="8.81640625" hidden="1"/>
+    <col min="5893" max="6144" width="8.85546875" hidden="1"/>
     <col min="6145" max="6145" width="27" hidden="1"/>
-    <col min="6146" max="6146" width="35.1796875" hidden="1"/>
-    <col min="6147" max="6147" width="23.7265625" hidden="1"/>
+    <col min="6146" max="6146" width="35.140625" hidden="1"/>
+    <col min="6147" max="6147" width="23.7109375" hidden="1"/>
     <col min="6148" max="6148" width="43" hidden="1"/>
-    <col min="6149" max="6400" width="8.81640625" hidden="1"/>
+    <col min="6149" max="6400" width="8.85546875" hidden="1"/>
     <col min="6401" max="6401" width="27" hidden="1"/>
-    <col min="6402" max="6402" width="35.1796875" hidden="1"/>
-    <col min="6403" max="6403" width="23.7265625" hidden="1"/>
+    <col min="6402" max="6402" width="35.140625" hidden="1"/>
+    <col min="6403" max="6403" width="23.7109375" hidden="1"/>
     <col min="6404" max="6404" width="43" hidden="1"/>
-    <col min="6405" max="6656" width="8.81640625" hidden="1"/>
+    <col min="6405" max="6656" width="8.85546875" hidden="1"/>
     <col min="6657" max="6657" width="27" hidden="1"/>
-    <col min="6658" max="6658" width="35.1796875" hidden="1"/>
-    <col min="6659" max="6659" width="23.7265625" hidden="1"/>
+    <col min="6658" max="6658" width="35.140625" hidden="1"/>
+    <col min="6659" max="6659" width="23.7109375" hidden="1"/>
     <col min="6660" max="6660" width="43" hidden="1"/>
-    <col min="6661" max="6912" width="8.81640625" hidden="1"/>
+    <col min="6661" max="6912" width="8.85546875" hidden="1"/>
     <col min="6913" max="6913" width="27" hidden="1"/>
-    <col min="6914" max="6914" width="35.1796875" hidden="1"/>
-    <col min="6915" max="6915" width="23.7265625" hidden="1"/>
+    <col min="6914" max="6914" width="35.140625" hidden="1"/>
+    <col min="6915" max="6915" width="23.7109375" hidden="1"/>
     <col min="6916" max="6916" width="43" hidden="1"/>
-    <col min="6917" max="7168" width="8.81640625" hidden="1"/>
+    <col min="6917" max="7168" width="8.85546875" hidden="1"/>
     <col min="7169" max="7169" width="27" hidden="1"/>
-    <col min="7170" max="7170" width="35.1796875" hidden="1"/>
-    <col min="7171" max="7171" width="23.7265625" hidden="1"/>
+    <col min="7170" max="7170" width="35.140625" hidden="1"/>
+    <col min="7171" max="7171" width="23.7109375" hidden="1"/>
     <col min="7172" max="7172" width="43" hidden="1"/>
-    <col min="7173" max="7424" width="8.81640625" hidden="1"/>
+    <col min="7173" max="7424" width="8.85546875" hidden="1"/>
     <col min="7425" max="7425" width="27" hidden="1"/>
-    <col min="7426" max="7426" width="35.1796875" hidden="1"/>
-    <col min="7427" max="7427" width="23.7265625" hidden="1"/>
+    <col min="7426" max="7426" width="35.140625" hidden="1"/>
+    <col min="7427" max="7427" width="23.7109375" hidden="1"/>
     <col min="7428" max="7428" width="43" hidden="1"/>
-    <col min="7429" max="7680" width="8.81640625" hidden="1"/>
+    <col min="7429" max="7680" width="8.85546875" hidden="1"/>
     <col min="7681" max="7681" width="27" hidden="1"/>
-    <col min="7682" max="7682" width="35.1796875" hidden="1"/>
-    <col min="7683" max="7683" width="23.7265625" hidden="1"/>
+    <col min="7682" max="7682" width="35.140625" hidden="1"/>
+    <col min="7683" max="7683" width="23.7109375" hidden="1"/>
     <col min="7684" max="7684" width="43" hidden="1"/>
-    <col min="7685" max="7936" width="8.81640625" hidden="1"/>
+    <col min="7685" max="7936" width="8.85546875" hidden="1"/>
     <col min="7937" max="7937" width="27" hidden="1"/>
-    <col min="7938" max="7938" width="35.1796875" hidden="1"/>
-    <col min="7939" max="7939" width="23.7265625" hidden="1"/>
+    <col min="7938" max="7938" width="35.140625" hidden="1"/>
+    <col min="7939" max="7939" width="23.7109375" hidden="1"/>
     <col min="7940" max="7940" width="43" hidden="1"/>
-    <col min="7941" max="8192" width="8.81640625" hidden="1"/>
+    <col min="7941" max="8192" width="8.85546875" hidden="1"/>
     <col min="8193" max="8193" width="27" hidden="1"/>
-    <col min="8194" max="8194" width="35.1796875" hidden="1"/>
-    <col min="8195" max="8195" width="23.7265625" hidden="1"/>
+    <col min="8194" max="8194" width="35.140625" hidden="1"/>
+    <col min="8195" max="8195" width="23.7109375" hidden="1"/>
     <col min="8196" max="8196" width="43" hidden="1"/>
-    <col min="8197" max="8448" width="8.81640625" hidden="1"/>
+    <col min="8197" max="8448" width="8.85546875" hidden="1"/>
     <col min="8449" max="8449" width="27" hidden="1"/>
-    <col min="8450" max="8450" width="35.1796875" hidden="1"/>
-    <col min="8451" max="8451" width="23.7265625" hidden="1"/>
+    <col min="8450" max="8450" width="35.140625" hidden="1"/>
+    <col min="8451" max="8451" width="23.7109375" hidden="1"/>
     <col min="8452" max="8452" width="43" hidden="1"/>
-    <col min="8453" max="8704" width="8.81640625" hidden="1"/>
+    <col min="8453" max="8704" width="8.85546875" hidden="1"/>
     <col min="8705" max="8705" width="27" hidden="1"/>
-    <col min="8706" max="8706" width="35.1796875" hidden="1"/>
-    <col min="8707" max="8707" width="23.7265625" hidden="1"/>
+    <col min="8706" max="8706" width="35.140625" hidden="1"/>
+    <col min="8707" max="8707" width="23.7109375" hidden="1"/>
     <col min="8708" max="8708" width="43" hidden="1"/>
-    <col min="8709" max="8960" width="8.81640625" hidden="1"/>
+    <col min="8709" max="8960" width="8.85546875" hidden="1"/>
     <col min="8961" max="8961" width="27" hidden="1"/>
-    <col min="8962" max="8962" width="35.1796875" hidden="1"/>
-    <col min="8963" max="8963" width="23.7265625" hidden="1"/>
+    <col min="8962" max="8962" width="35.140625" hidden="1"/>
+    <col min="8963" max="8963" width="23.7109375" hidden="1"/>
     <col min="8964" max="8964" width="43" hidden="1"/>
-    <col min="8965" max="9216" width="8.81640625" hidden="1"/>
+    <col min="8965" max="9216" width="8.85546875" hidden="1"/>
     <col min="9217" max="9217" width="27" hidden="1"/>
-    <col min="9218" max="9218" width="35.1796875" hidden="1"/>
-    <col min="9219" max="9219" width="23.7265625" hidden="1"/>
+    <col min="9218" max="9218" width="35.140625" hidden="1"/>
+    <col min="9219" max="9219" width="23.7109375" hidden="1"/>
     <col min="9220" max="9220" width="43" hidden="1"/>
-    <col min="9221" max="9472" width="8.81640625" hidden="1"/>
+    <col min="9221" max="9472" width="8.85546875" hidden="1"/>
     <col min="9473" max="9473" width="27" hidden="1"/>
-    <col min="9474" max="9474" width="35.1796875" hidden="1"/>
-    <col min="9475" max="9475" width="23.7265625" hidden="1"/>
+    <col min="9474" max="9474" width="35.140625" hidden="1"/>
+    <col min="9475" max="9475" width="23.7109375" hidden="1"/>
     <col min="9476" max="9476" width="43" hidden="1"/>
-    <col min="9477" max="9728" width="8.81640625" hidden="1"/>
+    <col min="9477" max="9728" width="8.85546875" hidden="1"/>
     <col min="9729" max="9729" width="27" hidden="1"/>
-    <col min="9730" max="9730" width="35.1796875" hidden="1"/>
-    <col min="9731" max="9731" width="23.7265625" hidden="1"/>
+    <col min="9730" max="9730" width="35.140625" hidden="1"/>
+    <col min="9731" max="9731" width="23.7109375" hidden="1"/>
     <col min="9732" max="9732" width="43" hidden="1"/>
-    <col min="9733" max="9984" width="8.81640625" hidden="1"/>
+    <col min="9733" max="9984" width="8.85546875" hidden="1"/>
     <col min="9985" max="9985" width="27" hidden="1"/>
-    <col min="9986" max="9986" width="35.1796875" hidden="1"/>
-    <col min="9987" max="9987" width="23.7265625" hidden="1"/>
+    <col min="9986" max="9986" width="35.140625" hidden="1"/>
+    <col min="9987" max="9987" width="23.7109375" hidden="1"/>
     <col min="9988" max="9988" width="43" hidden="1"/>
-    <col min="9989" max="10240" width="8.81640625" hidden="1"/>
+    <col min="9989" max="10240" width="8.85546875" hidden="1"/>
     <col min="10241" max="10241" width="27" hidden="1"/>
-    <col min="10242" max="10242" width="35.1796875" hidden="1"/>
-    <col min="10243" max="10243" width="23.7265625" hidden="1"/>
+    <col min="10242" max="10242" width="35.140625" hidden="1"/>
+    <col min="10243" max="10243" width="23.7109375" hidden="1"/>
     <col min="10244" max="10244" width="43" hidden="1"/>
-    <col min="10245" max="10496" width="8.81640625" hidden="1"/>
+    <col min="10245" max="10496" width="8.85546875" hidden="1"/>
     <col min="10497" max="10497" width="27" hidden="1"/>
-    <col min="10498" max="10498" width="35.1796875" hidden="1"/>
-    <col min="10499" max="10499" width="23.7265625" hidden="1"/>
+    <col min="10498" max="10498" width="35.140625" hidden="1"/>
+    <col min="10499" max="10499" width="23.7109375" hidden="1"/>
     <col min="10500" max="10500" width="43" hidden="1"/>
-    <col min="10501" max="10752" width="8.81640625" hidden="1"/>
+    <col min="10501" max="10752" width="8.85546875" hidden="1"/>
     <col min="10753" max="10753" width="27" hidden="1"/>
-    <col min="10754" max="10754" width="35.1796875" hidden="1"/>
-    <col min="10755" max="10755" width="23.7265625" hidden="1"/>
+    <col min="10754" max="10754" width="35.140625" hidden="1"/>
+    <col min="10755" max="10755" width="23.7109375" hidden="1"/>
     <col min="10756" max="10756" width="43" hidden="1"/>
-    <col min="10757" max="11008" width="8.81640625" hidden="1"/>
+    <col min="10757" max="11008" width="8.85546875" hidden="1"/>
     <col min="11009" max="11009" width="27" hidden="1"/>
-    <col min="11010" max="11010" width="35.1796875" hidden="1"/>
-    <col min="11011" max="11011" width="23.7265625" hidden="1"/>
+    <col min="11010" max="11010" width="35.140625" hidden="1"/>
+    <col min="11011" max="11011" width="23.7109375" hidden="1"/>
     <col min="11012" max="11012" width="43" hidden="1"/>
-    <col min="11013" max="11264" width="8.81640625" hidden="1"/>
+    <col min="11013" max="11264" width="8.85546875" hidden="1"/>
     <col min="11265" max="11265" width="27" hidden="1"/>
-    <col min="11266" max="11266" width="35.1796875" hidden="1"/>
-    <col min="11267" max="11267" width="23.7265625" hidden="1"/>
+    <col min="11266" max="11266" width="35.140625" hidden="1"/>
+    <col min="11267" max="11267" width="23.7109375" hidden="1"/>
     <col min="11268" max="11268" width="43" hidden="1"/>
-    <col min="11269" max="11520" width="8.81640625" hidden="1"/>
+    <col min="11269" max="11520" width="8.85546875" hidden="1"/>
     <col min="11521" max="11521" width="27" hidden="1"/>
-    <col min="11522" max="11522" width="35.1796875" hidden="1"/>
-    <col min="11523" max="11523" width="23.7265625" hidden="1"/>
+    <col min="11522" max="11522" width="35.140625" hidden="1"/>
+    <col min="11523" max="11523" width="23.7109375" hidden="1"/>
     <col min="11524" max="11524" width="43" hidden="1"/>
-    <col min="11525" max="11776" width="8.81640625" hidden="1"/>
+    <col min="11525" max="11776" width="8.85546875" hidden="1"/>
     <col min="11777" max="11777" width="27" hidden="1"/>
-    <col min="11778" max="11778" width="35.1796875" hidden="1"/>
-    <col min="11779" max="11779" width="23.7265625" hidden="1"/>
+    <col min="11778" max="11778" width="35.140625" hidden="1"/>
+    <col min="11779" max="11779" width="23.7109375" hidden="1"/>
     <col min="11780" max="11780" width="43" hidden="1"/>
-    <col min="11781" max="12032" width="8.81640625" hidden="1"/>
+    <col min="11781" max="12032" width="8.85546875" hidden="1"/>
     <col min="12033" max="12033" width="27" hidden="1"/>
-    <col min="12034" max="12034" width="35.1796875" hidden="1"/>
-    <col min="12035" max="12035" width="23.7265625" hidden="1"/>
+    <col min="12034" max="12034" width="35.140625" hidden="1"/>
+    <col min="12035" max="12035" width="23.7109375" hidden="1"/>
     <col min="12036" max="12036" width="43" hidden="1"/>
-    <col min="12037" max="12288" width="8.81640625" hidden="1"/>
+    <col min="12037" max="12288" width="8.85546875" hidden="1"/>
     <col min="12289" max="12289" width="27" hidden="1"/>
-    <col min="12290" max="12290" width="35.1796875" hidden="1"/>
-    <col min="12291" max="12291" width="23.7265625" hidden="1"/>
+    <col min="12290" max="12290" width="35.140625" hidden="1"/>
+    <col min="12291" max="12291" width="23.7109375" hidden="1"/>
     <col min="12292" max="12292" width="43" hidden="1"/>
-    <col min="12293" max="12544" width="8.81640625" hidden="1"/>
+    <col min="12293" max="12544" width="8.85546875" hidden="1"/>
     <col min="12545" max="12545" width="27" hidden="1"/>
-    <col min="12546" max="12546" width="35.1796875" hidden="1"/>
-    <col min="12547" max="12547" width="23.7265625" hidden="1"/>
+    <col min="12546" max="12546" width="35.140625" hidden="1"/>
+    <col min="12547" max="12547" width="23.7109375" hidden="1"/>
     <col min="12548" max="12548" width="43" hidden="1"/>
-    <col min="12549" max="12800" width="8.81640625" hidden="1"/>
+    <col min="12549" max="12800" width="8.85546875" hidden="1"/>
     <col min="12801" max="12801" width="27" hidden="1"/>
-    <col min="12802" max="12802" width="35.1796875" hidden="1"/>
-    <col min="12803" max="12803" width="23.7265625" hidden="1"/>
+    <col min="12802" max="12802" width="35.140625" hidden="1"/>
+    <col min="12803" max="12803" width="23.7109375" hidden="1"/>
     <col min="12804" max="12804" width="43" hidden="1"/>
-    <col min="12805" max="13056" width="8.81640625" hidden="1"/>
+    <col min="12805" max="13056" width="8.85546875" hidden="1"/>
     <col min="13057" max="13057" width="27" hidden="1"/>
-    <col min="13058" max="13058" width="35.1796875" hidden="1"/>
-    <col min="13059" max="13059" width="23.7265625" hidden="1"/>
+    <col min="13058" max="13058" width="35.140625" hidden="1"/>
+    <col min="13059" max="13059" width="23.7109375" hidden="1"/>
     <col min="13060" max="13060" width="43" hidden="1"/>
-    <col min="13061" max="13312" width="8.81640625" hidden="1"/>
+    <col min="13061" max="13312" width="8.85546875" hidden="1"/>
     <col min="13313" max="13313" width="27" hidden="1"/>
-    <col min="13314" max="13314" width="35.1796875" hidden="1"/>
-    <col min="13315" max="13315" width="23.7265625" hidden="1"/>
+    <col min="13314" max="13314" width="35.140625" hidden="1"/>
+    <col min="13315" max="13315" width="23.7109375" hidden="1"/>
     <col min="13316" max="13316" width="43" hidden="1"/>
-    <col min="13317" max="13568" width="8.81640625" hidden="1"/>
+    <col min="13317" max="13568" width="8.85546875" hidden="1"/>
     <col min="13569" max="13569" width="27" hidden="1"/>
-    <col min="13570" max="13570" width="35.1796875" hidden="1"/>
-    <col min="13571" max="13571" width="23.7265625" hidden="1"/>
+    <col min="13570" max="13570" width="35.140625" hidden="1"/>
+    <col min="13571" max="13571" width="23.7109375" hidden="1"/>
     <col min="13572" max="13572" width="43" hidden="1"/>
-    <col min="13573" max="13824" width="8.81640625" hidden="1"/>
+    <col min="13573" max="13824" width="8.85546875" hidden="1"/>
     <col min="13825" max="13825" width="27" hidden="1"/>
-    <col min="13826" max="13826" width="35.1796875" hidden="1"/>
-    <col min="13827" max="13827" width="23.7265625" hidden="1"/>
+    <col min="13826" max="13826" width="35.140625" hidden="1"/>
+    <col min="13827" max="13827" width="23.7109375" hidden="1"/>
     <col min="13828" max="13828" width="43" hidden="1"/>
-    <col min="13829" max="14080" width="8.81640625" hidden="1"/>
+    <col min="13829" max="14080" width="8.85546875" hidden="1"/>
     <col min="14081" max="14081" width="27" hidden="1"/>
-    <col min="14082" max="14082" width="35.1796875" hidden="1"/>
-    <col min="14083" max="14083" width="23.7265625" hidden="1"/>
+    <col min="14082" max="14082" width="35.140625" hidden="1"/>
+    <col min="14083" max="14083" width="23.7109375" hidden="1"/>
     <col min="14084" max="14084" width="43" hidden="1"/>
-    <col min="14085" max="14336" width="8.81640625" hidden="1"/>
+    <col min="14085" max="14336" width="8.85546875" hidden="1"/>
     <col min="14337" max="14337" width="27" hidden="1"/>
-    <col min="14338" max="14338" width="35.1796875" hidden="1"/>
-    <col min="14339" max="14339" width="23.7265625" hidden="1"/>
+    <col min="14338" max="14338" width="35.140625" hidden="1"/>
+    <col min="14339" max="14339" width="23.7109375" hidden="1"/>
     <col min="14340" max="14340" width="43" hidden="1"/>
-    <col min="14341" max="14592" width="8.81640625" hidden="1"/>
+    <col min="14341" max="14592" width="8.85546875" hidden="1"/>
     <col min="14593" max="14593" width="27" hidden="1"/>
-    <col min="14594" max="14594" width="35.1796875" hidden="1"/>
-    <col min="14595" max="14595" width="23.7265625" hidden="1"/>
+    <col min="14594" max="14594" width="35.140625" hidden="1"/>
+    <col min="14595" max="14595" width="23.7109375" hidden="1"/>
     <col min="14596" max="14596" width="43" hidden="1"/>
-    <col min="14597" max="14848" width="8.81640625" hidden="1"/>
+    <col min="14597" max="14848" width="8.85546875" hidden="1"/>
     <col min="14849" max="14849" width="27" hidden="1"/>
-    <col min="14850" max="14850" width="35.1796875" hidden="1"/>
-    <col min="14851" max="14851" width="23.7265625" hidden="1"/>
+    <col min="14850" max="14850" width="35.140625" hidden="1"/>
+    <col min="14851" max="14851" width="23.7109375" hidden="1"/>
     <col min="14852" max="14852" width="43" hidden="1"/>
-    <col min="14853" max="15104" width="8.81640625" hidden="1"/>
+    <col min="14853" max="15104" width="8.85546875" hidden="1"/>
     <col min="15105" max="15105" width="27" hidden="1"/>
-    <col min="15106" max="15106" width="35.1796875" hidden="1"/>
-    <col min="15107" max="15107" width="23.7265625" hidden="1"/>
+    <col min="15106" max="15106" width="35.140625" hidden="1"/>
+    <col min="15107" max="15107" width="23.7109375" hidden="1"/>
     <col min="15108" max="15108" width="43" hidden="1"/>
-    <col min="15109" max="15360" width="8.81640625" hidden="1"/>
+    <col min="15109" max="15360" width="8.85546875" hidden="1"/>
     <col min="15361" max="15361" width="27" hidden="1"/>
-    <col min="15362" max="15362" width="35.1796875" hidden="1"/>
-    <col min="15363" max="15363" width="23.7265625" hidden="1"/>
+    <col min="15362" max="15362" width="35.140625" hidden="1"/>
+    <col min="15363" max="15363" width="23.7109375" hidden="1"/>
     <col min="15364" max="15364" width="43" hidden="1"/>
-    <col min="15365" max="15616" width="8.81640625" hidden="1"/>
+    <col min="15365" max="15616" width="8.85546875" hidden="1"/>
     <col min="15617" max="15617" width="27" hidden="1"/>
-    <col min="15618" max="15618" width="35.1796875" hidden="1"/>
-    <col min="15619" max="15619" width="23.7265625" hidden="1"/>
+    <col min="15618" max="15618" width="35.140625" hidden="1"/>
+    <col min="15619" max="15619" width="23.7109375" hidden="1"/>
     <col min="15620" max="15620" width="43" hidden="1"/>
-    <col min="15621" max="15872" width="8.81640625" hidden="1"/>
+    <col min="15621" max="15872" width="8.85546875" hidden="1"/>
     <col min="15873" max="15873" width="27" hidden="1"/>
-    <col min="15874" max="15874" width="35.1796875" hidden="1"/>
-    <col min="15875" max="15875" width="23.7265625" hidden="1"/>
+    <col min="15874" max="15874" width="35.140625" hidden="1"/>
+    <col min="15875" max="15875" width="23.7109375" hidden="1"/>
     <col min="15876" max="15876" width="43" hidden="1"/>
-    <col min="15877" max="16128" width="8.81640625" hidden="1"/>
+    <col min="15877" max="16128" width="8.85546875" hidden="1"/>
     <col min="16129" max="16129" width="27" hidden="1"/>
-    <col min="16130" max="16130" width="35.1796875" hidden="1"/>
-    <col min="16131" max="16131" width="23.7265625" hidden="1"/>
+    <col min="16130" max="16130" width="35.140625" hidden="1"/>
+    <col min="16131" max="16131" width="23.7109375" hidden="1"/>
     <col min="16132" max="16132" width="43" hidden="1"/>
-    <col min="16133" max="16384" width="8.81640625" hidden="1"/>
+    <col min="16133" max="16384" width="8.85546875" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
-    </row>
-    <row r="2" spans="1:4" ht="19" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+    </row>
+    <row r="2" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>47</v>
-      </c>
+      <c r="B4" s="34"/>
       <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>46</v>
-      </c>
+      <c r="B5" s="34"/>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="B6" s="6"/>
       <c r="C6" s="16" t="s">
         <v>9</v>
       </c>
@@ -1688,51 +1566,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="6"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>51</v>
-      </c>
+      <c r="B8" s="34"/>
       <c r="C8" s="29"/>
       <c r="D8" s="30"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
         <v>15</v>
       </c>
@@ -1740,33 +1605,29 @@
       <c r="C11" s="7"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="31">
-        <v>46066</v>
-      </c>
+      <c r="B12" s="31"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="32">
-        <v>46095</v>
-      </c>
+      <c r="B13" s="32"/>
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
+    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
       <c r="C14" s="10"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
@@ -1776,55 +1637,41 @@
       </c>
       <c r="D15" s="19"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="12"/>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>55</v>
-      </c>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
       <c r="B17" s="12"/>
-      <c r="C17" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="C17" s="11"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>56</v>
-      </c>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
       <c r="B18" s="12"/>
-      <c r="C18" s="11" t="s">
-        <v>56</v>
-      </c>
+      <c r="C18" s="11"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="11"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="11"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="13"/>
       <c r="D21" s="14"/>
     </row>
-    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>20</v>
       </c>
@@ -1834,59 +1681,42 @@
       </c>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>54</v>
-      </c>
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="15"/>
-      <c r="C23" s="47" t="s">
-        <v>61</v>
-      </c>
+      <c r="C23" s="35"/>
       <c r="D23" s="15"/>
     </row>
-    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>55</v>
-      </c>
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
       <c r="B24" s="12"/>
-      <c r="C24" s="47" t="s">
-        <v>57</v>
-      </c>
+      <c r="C24" s="35"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>56</v>
-      </c>
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="47" t="s">
-        <v>58</v>
-      </c>
+      <c r="C25" s="35"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="47" t="s">
-        <v>59</v>
-      </c>
+      <c r="C26" s="35"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="48" t="s">
-        <v>60</v>
-      </c>
+      <c r="C27" s="36"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="13"/>
       <c r="D28" s="14"/>
     </row>
-    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>22</v>
       </c>
@@ -1896,90 +1726,78 @@
       </c>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="34" t="s">
-        <v>66</v>
-      </c>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="34"/>
       <c r="B30" s="12"/>
-      <c r="C30" s="34" t="s">
-        <v>70</v>
-      </c>
+      <c r="C30" s="34"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>67</v>
-      </c>
+    <row r="31" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="33"/>
       <c r="B31" s="12"/>
-      <c r="C31" s="33" t="s">
-        <v>69</v>
-      </c>
+      <c r="C31" s="33"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="33" t="s">
-        <v>68</v>
-      </c>
+    <row r="32" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="33"/>
       <c r="B32" s="12"/>
-      <c r="C32" s="33" t="s">
-        <v>71</v>
-      </c>
+      <c r="C32" s="33"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33"/>
       <c r="B33" s="12"/>
       <c r="C33" s="33"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
       <c r="C34" s="11"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="13"/>
       <c r="D35" s="14"/>
     </row>
-    <row r="36" spans="1:4" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="42" t="s">
+    <row r="36" spans="1:4" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="44"/>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="46"/>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
@@ -1995,113 +1813,113 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9631D1CA-4449-4B4F-A86D-993F781ADBD5}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="165.81640625" style="24" customWidth="1"/>
-    <col min="2" max="16384" width="8.81640625" hidden="1"/>
+    <col min="1" max="1" width="165.85546875" style="24" customWidth="1"/>
+    <col min="2" max="16384" width="8.85546875" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="47" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
         <v>44</v>
       </c>
@@ -2124,15 +1942,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100403D94F5EFEDBA469CF5DC1FC5550876" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="35f98ff01629d2aafa83205be6600687">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="efc4398b-3f3a-43cd-a058-be1b0f6fc7f7" xmlns:ns3="9ecb46fa-abf2-4ab2-bb3f-f32995625af0" xmlns:ns4="ac261bc5-afcf-4463-84ba-67345f157700" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59dea54c05fed12d7e56bc4163d4013a" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="efc4398b-3f3a-43cd-a058-be1b0f6fc7f7"/>
@@ -2362,6 +2171,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22A3B998-AA31-4F84-8FF1-82D5FD826BA2}">
   <ds:schemaRefs>
@@ -2374,14 +2192,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{428FE31D-BCB9-4AED-8ED6-F384B0C5A016}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95077E35-080A-4327-AE21-16F800D465E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2399,4 +2209,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{428FE31D-BCB9-4AED-8ED6-F384B0C5A016}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>